--- a/backend/template/出库单模板.xlsx
+++ b/backend/template/出库单模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\PyProject\WarehouseManagement\backend\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E16177-BAB0-40DA-B426-22B9FFF2DAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D8C053-80A5-4634-95E7-877AA8FED8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,7 +127,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -150,15 +150,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -175,20 +166,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,56 +454,56 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.9296875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.73046875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="7.19921875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="10.73046875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.73046875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="6.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.9296875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="15" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="6.73046875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="7.19921875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="10.73046875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.73046875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="6.265625" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23.65" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="7" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
